--- a/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_TEMPLATE.xlsx
+++ b/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/ethylene/bio_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FB7899-D026-8041-AC99-4F3DA97B4F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2372CC1F-2B8A-F142-B2AD-93C8C1D262EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="23500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29400" yWindow="500" windowWidth="38400" windowHeight="23500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="108">
   <si>
     <t>Ethanol Upgrade Asset Parameters (normalized by MWh ethanol)</t>
   </si>
@@ -196,43 +196,19 @@
     <t>Diff. Between Methods</t>
   </si>
   <si>
-    <t>h2_consumption</t>
-  </si>
-  <si>
     <t>elec_consumption</t>
-  </si>
-  <si>
-    <t>elec_consumption - ethanol</t>
-  </si>
-  <si>
-    <t>elec_production - ethanol</t>
-  </si>
-  <si>
-    <t>biomass_consumption - ethanol</t>
   </si>
   <si>
     <t>natgas_consumption</t>
   </si>
   <si>
-    <t>natgas_consumption - ethanol</t>
-  </si>
-  <si>
     <t>investment_cost</t>
-  </si>
-  <si>
-    <t>investment_cost - ethanol</t>
   </si>
   <si>
     <t>fixed_om_cost</t>
   </si>
   <si>
-    <t>fixed_om_cost - ethanol</t>
-  </si>
-  <si>
     <t>variable_om_cost</t>
-  </si>
-  <si>
-    <t>variable_om_cost - ethanol</t>
   </si>
   <si>
     <t>CI</t>
@@ -368,6 +344,42 @@
   </si>
   <si>
     <t xml:space="preserve"> d</t>
+  </si>
+  <si>
+    <t>elec_consumption - ethanol prod.</t>
+  </si>
+  <si>
+    <t>elec_production - ethanol prod.</t>
+  </si>
+  <si>
+    <t>biomass_consumption - ethanol prod.</t>
+  </si>
+  <si>
+    <t>natgas_consumption - ethanol prod.</t>
+  </si>
+  <si>
+    <t>investment_cost - ethanol prod.</t>
+  </si>
+  <si>
+    <t>variable_om_cost - ethanol prod.</t>
+  </si>
+  <si>
+    <t>h2_consumption - ethanol upgrade</t>
+  </si>
+  <si>
+    <t>elec_consumption - ethanol upgrade</t>
+  </si>
+  <si>
+    <t>natgas_consumption - ethanol upgrade</t>
+  </si>
+  <si>
+    <t>investment_cost - ethanol upgrade</t>
+  </si>
+  <si>
+    <t>fixed_om_cost - ethanol upgrade</t>
+  </si>
+  <si>
+    <t>fixed_om_cost - ethanol prod.</t>
   </si>
 </sst>
 </file>
@@ -1039,10 +1051,10 @@
         <v>3</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="BI2" s="1" t="s">
         <v>4</v>
@@ -1101,16 +1113,16 @@
         <v>21</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>22</v>
@@ -1123,10 +1135,10 @@
       </c>
       <c r="Q3" s="17"/>
       <c r="R3" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>25</v>
@@ -1144,16 +1156,16 @@
         <v>29</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>30</v>
@@ -1208,140 +1220,140 @@
         <v>45</v>
       </c>
       <c r="AV3" s="4" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="AW3" s="4" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="AX3" s="4" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="AY3" s="4" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="AZ3" s="4" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="BA3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="BD3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BE3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BF3" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="BG3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BI3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BB3" s="4" t="s">
+      <c r="BJ3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BC3" s="4" t="s">
+      <c r="BK3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BD3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="BE3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BF3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="BH3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="BJ3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="BK3" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="BL3" s="6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="BM3" s="6" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="BN3" s="6" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="BO3" s="17"/>
       <c r="BP3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="BQ3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BR3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="BS3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BT3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="BU3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="BV3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="BW3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BY3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="BZ3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="CA3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="CB3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="CD3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="CE3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="BQ3" s="4" t="s">
+      <c r="CF3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="BR3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BS3" s="4" t="s">
+      <c r="CG3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="CH3" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="BT3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="BU3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="BV3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BW3" s="4" t="s">
+      <c r="CJ3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="CK3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="CL3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="BY3" s="7" t="s">
+      <c r="CM3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="BZ3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="CA3" s="7" t="s">
+      <c r="CN3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="CB3" s="7" t="s">
+      <c r="CP3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="CD3" s="7" t="s">
+      <c r="CR3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="CE3" s="7" t="s">
+      <c r="CS3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="CF3" s="7" t="s">
+      <c r="CT3" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="CG3" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="CH3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CJ3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="CK3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="CL3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="CM3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="CN3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="CP3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="CU3" s="2" t="s">
         <v>25</v>
@@ -1359,16 +1371,16 @@
         <v>29</v>
       </c>
       <c r="CZ3" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="DA3" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="DB3" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="DC3" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="DD3" s="2" t="s">
         <v>30</v>
@@ -1382,10 +1394,10 @@
     </row>
     <row r="4" spans="2:110" x14ac:dyDescent="0.2">
       <c r="B4" s="23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D4" s="24">
         <v>6</v>
@@ -1554,7 +1566,7 @@
         <v>11.38621511864168</v>
       </c>
       <c r="BF4" s="1">
-        <f t="shared" ref="BF4:BF7" si="10">BV4</f>
+        <f>BV4</f>
         <v>1.8811318187915865E-5</v>
       </c>
       <c r="BG4" s="1">
@@ -1562,7 +1574,7 @@
         <v>1.5799999994038241</v>
       </c>
       <c r="BH4" s="1">
-        <f t="shared" ref="BH4:BH7" si="11">BW4</f>
+        <f t="shared" ref="BH4:BH7" si="10">BW4</f>
         <v>-115.59341194270499</v>
       </c>
       <c r="BI4" s="1">
@@ -1683,10 +1695,10 @@
         <v>1</v>
       </c>
       <c r="CS4" s="13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="CT4" s="12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="CU4" s="26">
         <v>0</v>
@@ -1727,10 +1739,10 @@
     </row>
     <row r="5" spans="2:110" x14ac:dyDescent="0.2">
       <c r="B5" s="23" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D5" s="24">
         <v>6</v>
@@ -1899,7 +1911,7 @@
         <v>11.38621511864168</v>
       </c>
       <c r="BF5" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="BF4:BF7" si="11">BV5</f>
         <v>1.8811318187915865E-5</v>
       </c>
       <c r="BG5" s="1">
@@ -1907,7 +1919,7 @@
         <v>1.5799999994038241</v>
       </c>
       <c r="BH5" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-115.59341194270499</v>
       </c>
       <c r="BI5" s="1">
@@ -2028,10 +2040,10 @@
         <v>2</v>
       </c>
       <c r="CS5" s="13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="CT5" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="CU5" s="26">
         <v>0.2142</v>
@@ -2072,10 +2084,10 @@
     </row>
     <row r="6" spans="2:110" x14ac:dyDescent="0.2">
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D6" s="24">
         <v>6</v>
@@ -2244,7 +2256,7 @@
         <v>11.38621511864168</v>
       </c>
       <c r="BF6" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8811318187915865E-5</v>
       </c>
       <c r="BG6" s="1">
@@ -2252,7 +2264,7 @@
         <v>1.5799999994038241</v>
       </c>
       <c r="BH6" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-115.59341194270499</v>
       </c>
       <c r="BI6" s="1">
@@ -2373,10 +2385,10 @@
         <v>3</v>
       </c>
       <c r="CS6" s="13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="CT6" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="CU6" s="26">
         <v>0</v>
@@ -2417,10 +2429,10 @@
     </row>
     <row r="7" spans="2:110" x14ac:dyDescent="0.2">
       <c r="B7" s="23" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D7" s="24">
         <v>6</v>
@@ -2589,7 +2601,7 @@
         <v>11.38621511864168</v>
       </c>
       <c r="BF7" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8811318187915865E-5</v>
       </c>
       <c r="BG7" s="1">
@@ -2597,7 +2609,7 @@
         <v>1.5799999994038241</v>
       </c>
       <c r="BH7" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>-115.59341194270499</v>
       </c>
       <c r="BI7" s="1">
@@ -2718,10 +2730,10 @@
         <v>4</v>
       </c>
       <c r="CS7" s="13" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="CT7" s="12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="CU7" s="26">
         <v>0</v>
@@ -3020,10 +3032,10 @@
         <v>5</v>
       </c>
       <c r="CS8" s="13" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="CT8" s="12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="CU8" s="27">
         <v>0</v>
@@ -3322,10 +3334,10 @@
         <v>6</v>
       </c>
       <c r="CS9" s="13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="CT9" s="12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="CU9" s="26">
         <v>0</v>
@@ -4649,7 +4661,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CR14" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="2:110" x14ac:dyDescent="0.2">
@@ -18389,7 +18401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -18410,122 +18422,67 @@
     <col min="16" max="16" width="16.33203125" customWidth="1"/>
     <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="2.6640625" customWidth="1"/>
-    <col min="19" max="19" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="S1" s="19" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="20" t="s">
+      <c r="B2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="O2" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="P2" s="21" t="s">
         <v>53</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>61</v>
       </c>
       <c r="Q2" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="S2" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="W2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z2" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB2" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC2" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD2" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE2" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF2" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG2" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH2" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI2" s="22" t="s">
-        <v>44</v>
-      </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>lc_detailed!AQ4</f>
         <v>NCEN_Ethanol_Dehydration_NGfuel</v>
@@ -18595,60 +18552,8 @@
         <v>2086.4915749407496</v>
       </c>
       <c r="R3" s="25"/>
-      <c r="S3" t="str" cm="1">
-        <f t="array" ref="S3:AI34">_xlfn._xlws.SORT(A3:Q34, 17, 1)</f>
-        <v>NCEN_Ethanol_Dehydration_H2fuel</v>
-      </c>
-      <c r="T3">
-        <v>21.04417908178743</v>
-      </c>
-      <c r="U3">
-        <v>5.277701376988464</v>
-      </c>
-      <c r="V3">
-        <v>8.9389265026015838</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>708.74125202212304</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>69.293050880640109</v>
-      </c>
-      <c r="AA3">
-        <v>11.843235666463674</v>
-      </c>
-      <c r="AB3">
-        <v>8.8681928020199641E-5</v>
-      </c>
-      <c r="AC3">
-        <v>11.38621511864168</v>
-      </c>
-      <c r="AD3">
-        <v>1.8811318187915865E-5</v>
-      </c>
-      <c r="AE3">
-        <v>1.5799999994038241</v>
-      </c>
-      <c r="AF3">
-        <v>-115.59341194270499</v>
-      </c>
-      <c r="AG3">
-        <v>-157.87623771256997</v>
-      </c>
-      <c r="AH3">
-        <v>-135.02693176053481</v>
-      </c>
-      <c r="AI3">
-        <v>429.6080867260863</v>
-      </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>lc_detailed!AQ5</f>
         <v>NCEN_Ethanol_Dehydration_H2fuel</v>
@@ -18718,59 +18623,8 @@
         <v>429.6080867260863</v>
       </c>
       <c r="R4" s="25"/>
-      <c r="S4" t="str">
-        <v>CEN_Ethanol_Dehydration_H2fuel</v>
-      </c>
-      <c r="T4">
-        <v>21.185416959553866</v>
-      </c>
-      <c r="U4">
-        <v>5.1759687177694103</v>
-      </c>
-      <c r="V4">
-        <v>8.7666202846639099</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>708.74125202212304</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>69.723395098262856</v>
-      </c>
-      <c r="AA4">
-        <v>11.843235666463674</v>
-      </c>
-      <c r="AB4">
-        <v>8.8681928020199641E-5</v>
-      </c>
-      <c r="AC4">
-        <v>11.38621511864168</v>
-      </c>
-      <c r="AD4">
-        <v>1.8811318187915865E-5</v>
-      </c>
-      <c r="AE4">
-        <v>1.5799999994038241</v>
-      </c>
-      <c r="AF4">
-        <v>-115.59341194270499</v>
-      </c>
-      <c r="AG4">
-        <v>-157.63823800117009</v>
-      </c>
-      <c r="AH4">
-        <v>-135.02693176053481</v>
-      </c>
-      <c r="AI4">
-        <v>430.14362965571854</v>
-      </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>lc_detailed!AQ6</f>
         <v>CEN_Ethanol_Dehydration_NGfuel</v>
@@ -18840,59 +18694,8 @@
         <v>2087.0369124090234</v>
       </c>
       <c r="R5" s="25"/>
-      <c r="S5" t="str">
-        <v>NCEN_Ethanol_Dehydration_NGfuel</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>5.277701376988464</v>
-      </c>
-      <c r="V5">
-        <v>8.9389265026015838</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>708.74125202212304</v>
-      </c>
-      <c r="Y5">
-        <v>24.31889749231679</v>
-      </c>
-      <c r="Z5">
-        <v>69.293050880640109</v>
-      </c>
-      <c r="AA5">
-        <v>11.843235666463674</v>
-      </c>
-      <c r="AB5">
-        <v>8.8681928020199641E-5</v>
-      </c>
-      <c r="AC5">
-        <v>11.38621511864168</v>
-      </c>
-      <c r="AD5">
-        <v>1.8811318187915865E-5</v>
-      </c>
-      <c r="AE5">
-        <v>1.5799999994038241</v>
-      </c>
-      <c r="AF5">
-        <v>-115.59341194270499</v>
-      </c>
-      <c r="AG5">
-        <v>-157.87623771256997</v>
-      </c>
-      <c r="AH5">
-        <v>1518.5818380435992</v>
-      </c>
-      <c r="AI5">
-        <v>2086.4915749407496</v>
-      </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>lc_detailed!AQ7</f>
         <v>CEN_Ethanol_Dehydration_H2fuel</v>
@@ -18962,59 +18765,8 @@
         <v>430.14362965571854</v>
       </c>
       <c r="R6" s="25"/>
-      <c r="S6" t="str">
-        <v>CEN_Ethanol_Dehydration_NGfuel</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>5.1759687177694103</v>
-      </c>
-      <c r="V6">
-        <v>8.7666202846639099</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>708.74125202212304</v>
-      </c>
-      <c r="Y6">
-        <v>24.469929908724691</v>
-      </c>
-      <c r="Z6">
-        <v>69.723395098262856</v>
-      </c>
-      <c r="AA6">
-        <v>11.843235666463674</v>
-      </c>
-      <c r="AB6">
-        <v>8.8681928020199641E-5</v>
-      </c>
-      <c r="AC6">
-        <v>11.38621511864168</v>
-      </c>
-      <c r="AD6">
-        <v>1.8811318187915865E-5</v>
-      </c>
-      <c r="AE6">
-        <v>1.5799999994038241</v>
-      </c>
-      <c r="AF6">
-        <v>-115.59341194270499</v>
-      </c>
-      <c r="AG6">
-        <v>-157.63823800117009</v>
-      </c>
-      <c r="AH6">
-        <v>1518.5818380435992</v>
-      </c>
-      <c r="AI6">
-        <v>2087.0369124090234</v>
-      </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <f>lc_detailed!AQ8</f>
         <v>0</v>
@@ -19084,59 +18836,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R7" s="25"/>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH7" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI7" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8">
         <f>lc_detailed!AQ9</f>
         <v>0</v>
@@ -19206,59 +18907,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R8" s="25"/>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH8" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI8" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9">
         <f>lc_detailed!AQ10</f>
         <v>0</v>
@@ -19328,59 +18978,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R9" s="25"/>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH9" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI9" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10">
         <f>lc_detailed!AQ11</f>
         <v>0</v>
@@ -19450,59 +19049,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R10" s="25"/>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH10" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI10" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11">
         <f>lc_detailed!AQ12</f>
         <v>0</v>
@@ -19572,59 +19120,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R11" s="25"/>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI11" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12">
         <f>lc_detailed!AQ13</f>
         <v>0</v>
@@ -19694,59 +19191,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R12" s="25"/>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH12" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI12" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13">
         <f>lc_detailed!AQ14</f>
         <v>0</v>
@@ -19816,59 +19262,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R13" s="25"/>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH13" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI13" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14">
         <f>lc_detailed!AQ15</f>
         <v>0</v>
@@ -19938,59 +19333,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R14" s="25"/>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH14" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI14" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
         <f>lc_detailed!AQ16</f>
         <v>0</v>
@@ -20060,59 +19404,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R15" s="25"/>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH15" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI15" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16">
         <f>lc_detailed!AQ17</f>
         <v>0</v>
@@ -20182,59 +19475,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R16" s="25"/>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH16" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI16" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17">
         <f>lc_detailed!AQ18</f>
         <v>0</v>
@@ -20304,59 +19546,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R17" s="25"/>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH17" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI17" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18">
         <f>lc_detailed!AQ19</f>
         <v>0</v>
@@ -20426,59 +19617,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R18" s="25"/>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH18" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI18" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19">
         <f>lc_detailed!AQ20</f>
         <v>0</v>
@@ -20548,59 +19688,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R19" s="25"/>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH19" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI19" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20">
         <f>lc_detailed!AQ21</f>
         <v>0</v>
@@ -20670,59 +19759,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R20" s="25"/>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH20" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI20" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21">
         <f>lc_detailed!AQ22</f>
         <v>0</v>
@@ -20792,59 +19830,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R21" s="25"/>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH21" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI21" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22">
         <f>lc_detailed!AQ23</f>
         <v>0</v>
@@ -20914,59 +19901,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R22" s="25"/>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH22" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI22" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23">
         <f>lc_detailed!AQ24</f>
         <v>0</v>
@@ -21036,59 +19972,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R23" s="25"/>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH23" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI23" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24">
         <f>lc_detailed!AQ25</f>
         <v>0</v>
@@ -21158,59 +20043,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R24" s="25"/>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH24" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI24" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25">
         <f>lc_detailed!AQ26</f>
         <v>0</v>
@@ -21280,59 +20114,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R25" s="25"/>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH25" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI25" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26">
         <f>lc_detailed!AQ27</f>
         <v>0</v>
@@ -21402,59 +20185,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R26" s="25"/>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH26" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI26" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27">
         <f>lc_detailed!AQ28</f>
         <v>0</v>
@@ -21524,59 +20256,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R27" s="25"/>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH27" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI27" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28">
         <f>lc_detailed!AQ29</f>
         <v>0</v>
@@ -21645,59 +20326,8 @@
         <f>lc_detailed!AS29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH28" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI28" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29">
         <f>lc_detailed!AQ30</f>
         <v>0</v>
@@ -21766,59 +20396,8 @@
         <f>lc_detailed!AS30</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH29" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI29" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30">
         <f>lc_detailed!AQ31</f>
         <v>0</v>
@@ -21887,59 +20466,8 @@
         <f>lc_detailed!AS31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH30" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI30" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31">
         <f>lc_detailed!AQ32</f>
         <v>0</v>
@@ -22008,59 +20536,8 @@
         <f>lc_detailed!AS32</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH31" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI31" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32">
         <f>lc_detailed!AQ33</f>
         <v>0</v>
@@ -22129,59 +20606,8 @@
         <f>lc_detailed!AS33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH32" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI32" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33">
         <f>lc_detailed!AQ34</f>
         <v>0</v>
@@ -22250,59 +20676,8 @@
         <f>lc_detailed!AS34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH33" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI33" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34">
         <f>lc_detailed!AQ35</f>
         <v>0</v>
@@ -22371,59 +20746,8 @@
         <f>lc_detailed!AS35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH34" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI34" t="e">
-        <v>#DIV/0!</v>
-      </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35">
         <f>lc_detailed!AQ36</f>
         <v>0</v>
@@ -22493,7 +20817,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36">
         <f>lc_detailed!AQ37</f>
         <v>0</v>
@@ -22563,7 +20887,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37">
         <f>lc_detailed!AQ38</f>
         <v>0</v>
@@ -22633,7 +20957,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38">
         <f>lc_detailed!AQ39</f>
         <v>0</v>
@@ -22703,7 +21027,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39">
         <f>lc_detailed!AQ40</f>
         <v>0</v>
@@ -22773,7 +21097,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40">
         <f>lc_detailed!AQ41</f>
         <v>0</v>
@@ -22843,7 +21167,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41">
         <f>lc_detailed!AQ42</f>
         <v>0</v>
@@ -22913,7 +21237,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42">
         <f>lc_detailed!AQ43</f>
         <v>0</v>
@@ -22983,7 +21307,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43">
         <f>lc_detailed!AQ44</f>
         <v>0</v>
@@ -23053,7 +21377,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44">
         <f>lc_detailed!AQ45</f>
         <v>0</v>
@@ -23123,7 +21447,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45">
         <f>lc_detailed!AQ46</f>
         <v>0</v>
@@ -23193,7 +21517,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46">
         <f>lc_detailed!AQ47</f>
         <v>0</v>
@@ -23263,7 +21587,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47">
         <f>lc_detailed!AQ48</f>
         <v>0</v>
@@ -23333,7 +21657,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48">
         <f>lc_detailed!AQ49</f>
         <v>0</v>

--- a/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_TEMPLATE.xlsx
+++ b/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/ethylene/bio_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BD09CC-A486-C340-BA04-AACE09A1CFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAD3652-33D0-1043-B5C7-2A183C1B3819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lc_detailed" sheetId="1" r:id="rId1"/>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="AS4" s="11">
         <f t="shared" ref="AS4:AS7" si="2">SUM(AV4:BH4)+BJ4+BK4</f>
-        <v>2229.5485304091699</v>
+        <v>2248.711517266313</v>
       </c>
       <c r="AT4" s="11">
         <f t="shared" ref="AT4:AT7" si="3">SUM(AV4:BH4)+BM4+BN4</f>
-        <v>2229.5485304091699</v>
+        <v>2248.711517266313</v>
       </c>
       <c r="AU4" s="5">
         <f t="shared" ref="AU4:AU7" si="4">AS4-AT4</f>
@@ -1549,24 +1549,24 @@
         <v>-115.59341194270499</v>
       </c>
       <c r="BI4" s="1">
-        <f t="shared" ref="BI4:BI35" si="6">CI4+CJ4+CL4-CD4</f>
-        <v>20.599643700899243</v>
+        <f>SUM(CI4:CL4)-CD4</f>
+        <v>23.742500843756389</v>
       </c>
       <c r="BJ4" s="1">
-        <f t="shared" ref="BJ4:BJ35" si="7">(AG4+AH4)*-1*CJ4</f>
-        <v>-157.87623771256997</v>
+        <f>(AG4+AH4)*-1*(CJ4+CK4)</f>
+        <v>-370.40103371257004</v>
       </c>
       <c r="BK4" s="1">
         <f>BI4*AG4</f>
-        <v>1518.5818380435992</v>
+        <v>1750.2696209007422</v>
       </c>
       <c r="BL4" s="1">
-        <f t="shared" ref="BL4:BL35" si="8">CI4+CL4-CD4</f>
+        <f>CI4+CL4-CD4</f>
         <v>18.264939841767614</v>
       </c>
       <c r="BM4" s="1">
-        <f t="shared" ref="BM4:BM35" si="9">CJ4*AH4*-1</f>
-        <v>14.235422526137326</v>
+        <f>(CJ4+CK4)*AH4*-1</f>
+        <v>33.398409383280189</v>
       </c>
       <c r="BN4" s="1">
         <f>BL4*AG4</f>
@@ -1823,11 +1823,11 @@
       </c>
       <c r="AS5" s="11">
         <f t="shared" si="2"/>
-        <v>572.66504219450667</v>
+        <v>591.82802905164942</v>
       </c>
       <c r="AT5" s="11">
         <f t="shared" si="3"/>
-        <v>572.66504219450667</v>
+        <v>591.82802905164954</v>
       </c>
       <c r="AU5" s="5">
         <f t="shared" si="4"/>
@@ -1842,11 +1842,11 @@
         <v>5.277701376988464</v>
       </c>
       <c r="AX5" s="1">
-        <f t="shared" ref="AX5:AX7" si="10">BR5</f>
+        <f t="shared" ref="AX5:AX7" si="6">BR5</f>
         <v>8.9389265026015838</v>
       </c>
       <c r="AY5" s="1">
-        <f t="shared" ref="AY5:AY7" si="11">BQ5</f>
+        <f t="shared" ref="AY5:AY7" si="7">BQ5</f>
         <v>0</v>
       </c>
       <c r="AZ5" s="1">
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="BB5" s="1">
-        <f t="shared" ref="BB5:BB7" si="12">BT5</f>
+        <f t="shared" ref="BB5:BB7" si="8">BT5</f>
         <v>69.293050880640109</v>
       </c>
       <c r="BC5" s="1">
@@ -1866,7 +1866,7 @@
         <v>11.843235666463674</v>
       </c>
       <c r="BD5" s="1">
-        <f t="shared" ref="BD5:BD7" si="13">BU5</f>
+        <f t="shared" ref="BD5:BD7" si="9">BU5</f>
         <v>26.202941601965065</v>
       </c>
       <c r="BE5" s="1">
@@ -1874,7 +1874,7 @@
         <v>11.38621511864168</v>
       </c>
       <c r="BF5" s="1">
-        <f t="shared" ref="BF5:BF7" si="14">BV5</f>
+        <f t="shared" ref="BF5:BF7" si="10">BV5</f>
         <v>116.85412135970147</v>
       </c>
       <c r="BG5" s="1">
@@ -1882,28 +1882,28 @@
         <v>1.5799999994038241</v>
       </c>
       <c r="BH5" s="1">
-        <f t="shared" ref="BH5:BH7" si="15">BW5</f>
+        <f t="shared" ref="BH5:BH7" si="11">BW5</f>
         <v>-115.59341194270499</v>
       </c>
       <c r="BI5" s="1">
-        <f t="shared" si="6"/>
-        <v>-1.831647537597374</v>
+        <f t="shared" ref="BI5:BI66" si="12">SUM(CI5:CL5)-CD5</f>
+        <v>1.3112096052597693</v>
       </c>
       <c r="BJ5" s="1">
-        <f t="shared" si="7"/>
-        <v>-157.87623771256997</v>
+        <f t="shared" ref="BJ5:BJ66" si="13">(AG5+AH5)*-1*(CJ5+CK5)</f>
+        <v>-370.40103371257004</v>
       </c>
       <c r="BK5" s="1">
-        <f t="shared" ref="BK5:BK66" si="16">BI5*AG5</f>
-        <v>-135.02693176053481</v>
+        <f t="shared" ref="BK5:BK66" si="14">BI5*AG5</f>
+        <v>96.660851096608084</v>
       </c>
       <c r="BL5" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="BL5:BL66" si="15">CI5+CL5-CD5</f>
         <v>-4.1663513967290058</v>
       </c>
       <c r="BM5" s="1">
-        <f t="shared" si="9"/>
-        <v>14.235422526137326</v>
+        <f t="shared" ref="BM5:BM66" si="16">(CJ5+CK5)*AH5*-1</f>
+        <v>33.398409383280189</v>
       </c>
       <c r="BN5" s="1">
         <f t="shared" ref="BN5:BN66" si="17">BL5*AG5</f>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="AS6" s="11">
         <f t="shared" si="2"/>
-        <v>2230.0938678774437</v>
+        <v>2249.5772375917295</v>
       </c>
       <c r="AT6" s="11">
         <f t="shared" si="3"/>
-        <v>2230.0938678774437</v>
+        <v>2249.5772375917295</v>
       </c>
       <c r="AU6" s="5">
         <f t="shared" si="4"/>
@@ -2179,11 +2179,11 @@
         <v>5.1759687177694103</v>
       </c>
       <c r="AX6" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>8.7666202846639099</v>
       </c>
       <c r="AY6" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AZ6" s="1">
@@ -2195,7 +2195,7 @@
         <v>24.469929908724691</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>69.723395098262856</v>
       </c>
       <c r="BC6" s="1">
@@ -2203,7 +2203,7 @@
         <v>11.843235666463674</v>
       </c>
       <c r="BD6" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>26.202941601965065</v>
       </c>
       <c r="BE6" s="1">
@@ -2211,7 +2211,7 @@
         <v>11.38621511864168</v>
       </c>
       <c r="BF6" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>116.85412135970147</v>
       </c>
       <c r="BG6" s="1">
@@ -2219,28 +2219,28 @@
         <v>1.5799999994038241</v>
       </c>
       <c r="BH6" s="1">
+        <f t="shared" si="11"/>
+        <v>-115.59341194270499</v>
+      </c>
+      <c r="BI6" s="1">
+        <f t="shared" si="12"/>
+        <v>23.742500843756389</v>
+      </c>
+      <c r="BJ6" s="1">
+        <f t="shared" si="13"/>
+        <v>-369.84265114402729</v>
+      </c>
+      <c r="BK6" s="1">
+        <f t="shared" si="14"/>
+        <v>1750.2696209007422</v>
+      </c>
+      <c r="BL6" s="1">
         <f t="shared" si="15"/>
-        <v>-115.59341194270499</v>
-      </c>
-      <c r="BI6" s="1">
-        <f t="shared" si="6"/>
-        <v>20.599643700899243</v>
-      </c>
-      <c r="BJ6" s="1">
-        <f t="shared" si="7"/>
-        <v>-157.63823800117009</v>
-      </c>
-      <c r="BK6" s="1">
+        <v>18.264939841767614</v>
+      </c>
+      <c r="BM6" s="1">
         <f t="shared" si="16"/>
-        <v>1518.5818380435992</v>
-      </c>
-      <c r="BL6" s="1">
-        <f t="shared" si="8"/>
-        <v>18.264939841767614</v>
-      </c>
-      <c r="BM6" s="1">
-        <f t="shared" si="9"/>
-        <v>14.473422237537205</v>
+        <v>33.956791951822922</v>
       </c>
       <c r="BN6" s="1">
         <f t="shared" si="17"/>
@@ -2497,11 +2497,11 @@
       </c>
       <c r="AS7" s="11">
         <f t="shared" si="2"/>
-        <v>573.20058512413891</v>
+        <v>592.6839548384246</v>
       </c>
       <c r="AT7" s="11">
         <f t="shared" si="3"/>
-        <v>573.2005851241388</v>
+        <v>592.6839548384246</v>
       </c>
       <c r="AU7" s="5">
         <f t="shared" si="4"/>
@@ -2516,11 +2516,11 @@
         <v>5.1759687177694103</v>
       </c>
       <c r="AX7" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>8.7666202846639099</v>
       </c>
       <c r="AY7" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AZ7" s="1">
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="BB7" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>69.723395098262856</v>
       </c>
       <c r="BC7" s="1">
@@ -2540,7 +2540,7 @@
         <v>11.843235666463674</v>
       </c>
       <c r="BD7" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>26.202941601965065</v>
       </c>
       <c r="BE7" s="1">
@@ -2548,7 +2548,7 @@
         <v>11.38621511864168</v>
       </c>
       <c r="BF7" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>116.85412135970147</v>
       </c>
       <c r="BG7" s="1">
@@ -2556,28 +2556,28 @@
         <v>1.5799999994038241</v>
       </c>
       <c r="BH7" s="1">
+        <f t="shared" si="11"/>
+        <v>-115.59341194270499</v>
+      </c>
+      <c r="BI7" s="1">
+        <f t="shared" si="12"/>
+        <v>1.3112096052597693</v>
+      </c>
+      <c r="BJ7" s="1">
+        <f t="shared" si="13"/>
+        <v>-369.84265114402729</v>
+      </c>
+      <c r="BK7" s="1">
+        <f t="shared" si="14"/>
+        <v>96.660851096608084</v>
+      </c>
+      <c r="BL7" s="1">
         <f t="shared" si="15"/>
-        <v>-115.59341194270499</v>
-      </c>
-      <c r="BI7" s="1">
-        <f t="shared" si="6"/>
-        <v>-1.831647537597374</v>
-      </c>
-      <c r="BJ7" s="1">
-        <f t="shared" si="7"/>
-        <v>-157.63823800117009</v>
-      </c>
-      <c r="BK7" s="1">
+        <v>-4.1663513967290058</v>
+      </c>
+      <c r="BM7" s="1">
         <f t="shared" si="16"/>
-        <v>-135.02693176053481</v>
-      </c>
-      <c r="BL7" s="1">
-        <f t="shared" si="8"/>
-        <v>-4.1663513967290058</v>
-      </c>
-      <c r="BM7" s="1">
-        <f t="shared" si="9"/>
-        <v>14.473422237537205</v>
+        <v>33.956791951822922</v>
       </c>
       <c r="BN7" s="1">
         <f t="shared" si="17"/>
@@ -2854,23 +2854,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI8" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ8" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK8" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL8" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM8" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL8" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM8" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN8" s="1" t="e">
@@ -3148,23 +3148,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI9" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ9" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK9" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL9" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM9" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL9" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM9" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN9" s="1" t="e">
@@ -3442,23 +3442,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI10" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ10" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK10" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL10" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM10" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL10" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM10" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN10" s="1" t="e">
@@ -3691,23 +3691,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI11" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ11" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK11" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL11" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM11" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL11" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM11" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN11" s="1" t="e">
@@ -3940,23 +3940,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI12" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ12" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK12" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL12" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM12" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL12" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM12" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN12" s="1" t="e">
@@ -4189,23 +4189,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI13" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ13" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK13" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL13" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM13" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL13" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM13" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN13" s="1" t="e">
@@ -4438,23 +4438,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI14" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ14" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK14" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL14" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM14" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL14" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM14" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN14" s="1" t="e">
@@ -4687,23 +4687,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI15" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ15" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK15" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL15" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM15" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL15" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM15" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN15" s="1" t="e">
@@ -4936,23 +4936,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI16" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ16" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK16" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL16" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM16" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL16" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM16" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN16" s="1" t="e">
@@ -5185,23 +5185,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI17" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ17" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK17" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL17" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM17" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL17" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM17" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN17" s="1" t="e">
@@ -5434,23 +5434,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI18" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ18" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK18" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL18" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM18" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL18" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM18" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN18" s="1" t="e">
@@ -5683,23 +5683,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI19" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ19" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK19" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL19" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM19" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL19" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM19" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN19" s="1" t="e">
@@ -5932,23 +5932,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI20" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ20" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK20" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL20" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM20" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL20" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM20" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN20" s="1" t="e">
@@ -6181,23 +6181,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI21" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ21" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK21" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL21" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM21" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL21" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM21" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN21" s="1" t="e">
@@ -6430,23 +6430,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI22" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ22" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK22" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL22" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM22" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL22" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM22" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN22" s="1" t="e">
@@ -6679,23 +6679,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI23" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ23" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK23" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL23" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM23" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL23" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM23" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN23" s="1" t="e">
@@ -6928,23 +6928,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI24" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ24" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK24" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL24" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM24" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL24" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM24" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN24" s="1" t="e">
@@ -7177,23 +7177,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI25" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ25" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK25" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL25" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM25" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL25" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM25" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN25" s="1" t="e">
@@ -7426,23 +7426,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI26" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ26" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK26" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL26" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM26" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL26" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM26" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN26" s="1" t="e">
@@ -7676,23 +7676,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI27" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ27" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK27" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL27" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM27" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL27" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM27" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN27" s="1" t="e">
@@ -7925,23 +7925,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI28" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ28" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK28" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL28" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM28" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL28" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM28" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN28" s="1" t="e">
@@ -8174,23 +8174,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI29" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ29" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK29" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL29" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM29" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL29" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM29" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN29" s="1" t="e">
@@ -8423,23 +8423,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI30" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ30" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK30" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL30" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM30" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL30" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM30" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN30" s="1" t="e">
@@ -8672,23 +8672,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI31" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ31" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK31" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL31" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM31" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL31" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM31" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN31" s="1" t="e">
@@ -8921,23 +8921,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI32" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ32" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK32" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL32" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM32" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL32" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM32" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN32" s="1" t="e">
@@ -9170,23 +9170,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI33" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ33" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK33" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL33" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM33" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL33" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM33" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN33" s="1" t="e">
@@ -9419,23 +9419,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI34" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ34" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK34" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL34" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM34" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL34" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM34" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN34" s="1" t="e">
@@ -9668,23 +9668,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI35" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ35" s="1" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK35" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL35" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM35" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL35" s="1" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM35" s="1" t="e">
-        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN35" s="1" t="e">
@@ -9917,23 +9917,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI36" s="1" t="e">
-        <f t="shared" ref="BI36:BI66" si="54">CI36+CJ36+CL36-CD36</f>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ36" s="1" t="e">
-        <f t="shared" ref="BJ36:BJ66" si="55">(AG36+AH36)*-1*CJ36</f>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK36" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL36" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM36" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL36" s="1" t="e">
-        <f t="shared" ref="BL36:BL66" si="56">CI36+CL36-CD36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM36" s="1" t="e">
-        <f t="shared" ref="BM36:BM66" si="57">CJ36*AH36*-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="BN36" s="1" t="e">
@@ -10166,23 +10166,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI37" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ37" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK37" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL37" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM37" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL37" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM37" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN37" s="1" t="e">
@@ -10415,23 +10415,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI38" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ38" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK38" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL38" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM38" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL38" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM38" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN38" s="1" t="e">
@@ -10664,23 +10664,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI39" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ39" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK39" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL39" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM39" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL39" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM39" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN39" s="1" t="e">
@@ -10913,23 +10913,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI40" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ40" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK40" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL40" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM40" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL40" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM40" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN40" s="1" t="e">
@@ -11162,23 +11162,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI41" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ41" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK41" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL41" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM41" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL41" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM41" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN41" s="1" t="e">
@@ -11411,23 +11411,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI42" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ42" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK42" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL42" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM42" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL42" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM42" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN42" s="1" t="e">
@@ -11660,23 +11660,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI43" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ43" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK43" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL43" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM43" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL43" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM43" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN43" s="1" t="e">
@@ -11909,23 +11909,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI44" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ44" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK44" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL44" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM44" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL44" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM44" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN44" s="1" t="e">
@@ -12158,23 +12158,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI45" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ45" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK45" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL45" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM45" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL45" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM45" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN45" s="1" t="e">
@@ -12407,23 +12407,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI46" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ46" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK46" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL46" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM46" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL46" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM46" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN46" s="1" t="e">
@@ -12656,23 +12656,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI47" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ47" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK47" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL47" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM47" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL47" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM47" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN47" s="1" t="e">
@@ -12905,23 +12905,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI48" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ48" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK48" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL48" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM48" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL48" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM48" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN48" s="1" t="e">
@@ -13154,23 +13154,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI49" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ49" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK49" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL49" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM49" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL49" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM49" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN49" s="1" t="e">
@@ -13403,23 +13403,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI50" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ50" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK50" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL50" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM50" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL50" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM50" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN50" s="1" t="e">
@@ -13652,23 +13652,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI51" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ51" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK51" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL51" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM51" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL51" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM51" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN51" s="1" t="e">
@@ -13901,23 +13901,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI52" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ52" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK52" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL52" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM52" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL52" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM52" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN52" s="1" t="e">
@@ -14150,23 +14150,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI53" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ53" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK53" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL53" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM53" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL53" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM53" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN53" s="1" t="e">
@@ -14399,23 +14399,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI54" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ54" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK54" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL54" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM54" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL54" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM54" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN54" s="1" t="e">
@@ -14648,23 +14648,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI55" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ55" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK55" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL55" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM55" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL55" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM55" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN55" s="1" t="e">
@@ -14897,23 +14897,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI56" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ56" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK56" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL56" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM56" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL56" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM56" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN56" s="1" t="e">
@@ -15146,23 +15146,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI57" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ57" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK57" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL57" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM57" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL57" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM57" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN57" s="1" t="e">
@@ -15395,23 +15395,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI58" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ58" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK58" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL58" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM58" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL58" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM58" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN58" s="1" t="e">
@@ -15644,23 +15644,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI59" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ59" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK59" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL59" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM59" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL59" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM59" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN59" s="1" t="e">
@@ -15893,23 +15893,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI60" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ60" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK60" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL60" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM60" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL60" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM60" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN60" s="1" t="e">
@@ -16142,23 +16142,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI61" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ61" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK61" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL61" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM61" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL61" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM61" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN61" s="1" t="e">
@@ -16391,23 +16391,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI62" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ62" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK62" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL62" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM62" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL62" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM62" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN62" s="1" t="e">
@@ -16640,23 +16640,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI63" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ63" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK63" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL63" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM63" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL63" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM63" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN63" s="1" t="e">
@@ -16889,23 +16889,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI64" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ64" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK64" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL64" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM64" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL64" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM64" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN64" s="1" t="e">
@@ -17138,23 +17138,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI65" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ65" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK65" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL65" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM65" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL65" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM65" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN65" s="1" t="e">
@@ -17387,23 +17387,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BI66" s="1" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BJ66" s="1" t="e">
-        <f t="shared" si="55"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BK66" s="1" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BL66" s="1" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="BM66" s="1" t="e">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL66" s="1" t="e">
-        <f t="shared" si="56"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM66" s="1" t="e">
-        <f t="shared" si="57"/>
         <v>#DIV/0!</v>
       </c>
       <c r="BN66" s="1" t="e">
@@ -18005,15 +18005,15 @@
       </c>
       <c r="O3" s="25">
         <f>lc_detailed!BJ4</f>
-        <v>-157.87623771256997</v>
+        <v>-370.40103371257004</v>
       </c>
       <c r="P3" s="25">
         <f>lc_detailed!BK4</f>
-        <v>1518.5818380435992</v>
+        <v>1750.2696209007422</v>
       </c>
       <c r="Q3" s="25">
         <f>lc_detailed!AS4</f>
-        <v>2229.5485304091699</v>
+        <v>2248.711517266313</v>
       </c>
       <c r="R3" s="25"/>
     </row>
@@ -18076,15 +18076,15 @@
       </c>
       <c r="O4" s="25">
         <f>lc_detailed!BJ5</f>
-        <v>-157.87623771256997</v>
+        <v>-370.40103371257004</v>
       </c>
       <c r="P4" s="25">
         <f>lc_detailed!BK5</f>
-        <v>-135.02693176053481</v>
+        <v>96.660851096608084</v>
       </c>
       <c r="Q4" s="25">
         <f>lc_detailed!AS5</f>
-        <v>572.66504219450667</v>
+        <v>591.82802905164942</v>
       </c>
       <c r="R4" s="25"/>
     </row>
@@ -18147,15 +18147,15 @@
       </c>
       <c r="O5" s="25">
         <f>lc_detailed!BJ6</f>
-        <v>-157.63823800117009</v>
+        <v>-369.84265114402729</v>
       </c>
       <c r="P5" s="25">
         <f>lc_detailed!BK6</f>
-        <v>1518.5818380435992</v>
+        <v>1750.2696209007422</v>
       </c>
       <c r="Q5" s="25">
         <f>lc_detailed!AS6</f>
-        <v>2230.0938678774437</v>
+        <v>2249.5772375917295</v>
       </c>
       <c r="R5" s="25"/>
     </row>
@@ -18218,15 +18218,15 @@
       </c>
       <c r="O6" s="25">
         <f>lc_detailed!BJ7</f>
-        <v>-157.63823800117009</v>
+        <v>-369.84265114402729</v>
       </c>
       <c r="P6" s="25">
         <f>lc_detailed!BK7</f>
-        <v>-135.02693176053481</v>
+        <v>96.660851096608084</v>
       </c>
       <c r="Q6" s="25">
         <f>lc_detailed!AS7</f>
-        <v>573.20058512413891</v>
+        <v>592.6839548384246</v>
       </c>
       <c r="R6" s="25"/>
     </row>

--- a/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_TEMPLATE.xlsx
+++ b/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/ethylene/bio_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAD3652-33D0-1043-B5C7-2A183C1B3819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A536F05A-98DC-DA45-97FD-8C902C1DFC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
